--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/WEST_VIRGINIA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/WEST_VIRGINIA_2018.xlsx
@@ -391,7 +391,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="3">
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="20">
@@ -787,7 +787,7 @@
         <v>2</v>
       </c>
       <c r="D24">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="25">
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="D26">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="27">
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="29">
@@ -942,7 +942,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C33">
@@ -1129,7 +1129,7 @@
         <v>2</v>
       </c>
       <c r="D43">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="44">
@@ -1255,7 +1255,7 @@
         <v>2</v>
       </c>
       <c r="D50">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="51">
@@ -1417,7 +1417,7 @@
         <v>2</v>
       </c>
       <c r="D59">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="60">
@@ -1435,7 +1435,7 @@
         <v>2</v>
       </c>
       <c r="D60">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="61">
@@ -1561,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="D67">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="68">
@@ -1651,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="D72">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="73">
@@ -1831,7 +1831,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="83">
@@ -1849,7 +1849,7 @@
         <v>2</v>
       </c>
       <c r="D83">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="84">
@@ -1921,7 +1921,7 @@
         <v>2</v>
       </c>
       <c r="D87">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="88">
@@ -1939,7 +1939,7 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="89">
@@ -2137,7 +2137,7 @@
         <v>2</v>
       </c>
       <c r="D99">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="100">
@@ -2245,7 +2245,7 @@
         <v>2</v>
       </c>
       <c r="D105">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="106">
@@ -2263,7 +2263,7 @@
         <v>2</v>
       </c>
       <c r="D106">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="107">
@@ -2407,7 +2407,7 @@
         <v>2</v>
       </c>
       <c r="D114">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="115">
@@ -2443,7 +2443,7 @@
         <v>2</v>
       </c>
       <c r="D116">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="117">
@@ -2605,7 +2605,7 @@
         <v>2</v>
       </c>
       <c r="D125">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="126">
@@ -2677,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="D129">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="130">
@@ -2785,7 +2785,7 @@
         <v>2</v>
       </c>
       <c r="D135">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="136">
